--- a/docs/modeling_tracking.xlsx
+++ b/docs/modeling_tracking.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ep-cpien\OneDrive\GitHub\ds-ibmr-2025\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/cpien_usbr_gov/Documents/Work/GitHub/ds-ibmr-2025/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A487571F-DB4E-4054-8D97-CF66A75C1602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{A487571F-DB4E-4054-8D97-CF66A75C1602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B6AA61C-9C49-478B-8CCE-696E9BE02CAB}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="3105" windowWidth="21600" windowHeight="11385" xr2:uid="{4687259E-B190-4618-9252-1779CDEB9469}"/>
+    <workbookView xWindow="-23970" yWindow="4065" windowWidth="21600" windowHeight="11385" xr2:uid="{4687259E-B190-4618-9252-1779CDEB9469}"/>
   </bookViews>
   <sheets>
     <sheet name="modeling_tracking" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Alternative</t>
   </si>
@@ -83,6 +96,12 @@
   </si>
   <si>
     <t>alt1_status-quo_output.rds</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>alt2_status-quo_output.rds</t>
   </si>
 </sst>
 </file>
@@ -993,6 +1012,15 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1">
+        <v>45716</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
